--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/SOUTH_CAROLINA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/SOUTH_CAROLINA_2012.xlsx
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C157">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C563">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C654">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C655">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C692">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C693">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1177">
